--- a/jpcore-r4/feature/swg2_servicerequest/StructureDefinition-jp-medicationadministration-injection.xlsx
+++ b/jpcore-r4/feature/swg2_servicerequest/StructureDefinition-jp-medicationadministration-injection.xlsx
@@ -1011,7 +1011,7 @@
     <t>医薬品</t>
   </si>
   <si>
-    <t>投与された薬剤を識別する。既知の薬のリストから薬を識別するコード情報を設定する。</t>
+    <t>医薬品の識別情報は必須でありmedicationReference.referenceが必ず存在しなければならない、JP Coreでは注射の医薬品情報は単一薬剤の場合も Medicationリソースとして記述し、medicationCodeableConceptは使用しない。参照するMedicationリソースは、MedicationRequest.contained属性に内包することが望ましいが、外部参照としても良い。</t>
   </si>
   <si>
     <t>ひとつのtext要素と、複数のcoding 要素を記述できる。処方オーダ時に選択または入力し、実際に処方箋に印字される文字列を必ずtext要素に格納した上で、それをコード化した情報を1個以上のcoding 要素に記述する。  
